--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -1028,92 +1028,212 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="15">
-        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="15">
-        <f>IF(I8="","",1440-I8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="17" t="n"/>
+      <c r="A8" s="24" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>570</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>1260</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <t>Attended all classes today</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="15">
-        <f>IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="15">
-        <f>IF(I9="","",1440-I9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="17" t="n"/>
+      <c r="A9" s="24" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>560</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>1010</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>430</v>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>Utilized the time in revising lectures</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n"/>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
-      <c r="I10" s="15">
-        <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="15">
-        <f>IF(I10="","",1440-I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="16" t="n"/>
-      <c r="N10" s="17" t="n"/>
+      <c r="A10" s="24" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>560</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>740</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>Can't Attend classes but utilized time in my hobby</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
-      <c r="I11" s="15">
-        <f>IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="15">
-        <f>IF(I11="","",1440-I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="16" t="n"/>
-      <c r="N11" s="17" t="n"/>
+      <c r="A11" s="24" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>490</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>760</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>680</v>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>Was not having classes today overall day was good</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="n"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="41" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08B38FE9-44F6-492A-9BDA-BA5F94AA92D3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08B38FE9-44F6-492A-9BDA-BA5F94AA92D3}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A32DBFB7-01E4-41DD-8C6B-DFD6BF8849AA}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -237,6 +237,21 @@
   <si>
     <t>Utilized the Sunday in other activities and hobbies</t>
   </si>
+  <si>
+    <t>Attended family gathering on festival</t>
+  </si>
+  <si>
+    <t>Practiced For CA</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Attended all classes today and feeling tired</t>
+  </si>
+  <si>
+    <t>Utilized my day well</t>
+  </si>
 </sst>
 </file>
 
@@ -439,6 +454,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -446,8 +463,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,6 +559,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -931,74 +950,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="19"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="22">
         <v>12614066</v>
       </c>
-      <c r="G2" s="19"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1448,115 +1467,235 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>500</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>420</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>100</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>740</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>240</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>280</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>530</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>480</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>500</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>240</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>620</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>300</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>180</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
@@ -9840,11 +9979,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" ref="I396:I459" si="12">IF(SUM(B396:F396,H396)=0,"",SUM(B396:F396,H396))</f>
+        <f t="shared" ref="I396:I401" si="12">IF(SUM(B396:F396,H396)=0,"",SUM(B396:F396,H396))</f>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" ref="J396:J459" si="13">IF(I396="","",1440-I396)</f>
+        <f t="shared" ref="J396:J401" si="13">IF(I396="","",1440-I396)</f>
         <v/>
       </c>
       <c r="K396" s="16"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A32DBFB7-01E4-41DD-8C6B-DFD6BF8849AA}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08321064-23B5-4B61-ACC3-DCA9BAC814C3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Utilized my day well</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
 </sst>
 </file>
@@ -1698,70 +1701,142 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="14">
+        <v>550</v>
+      </c>
+      <c r="C20" s="14">
+        <v>120</v>
+      </c>
+      <c r="D20" s="14">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>180</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>240</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>230</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>450</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>480</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>470</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>60</v>
+      </c>
+      <c r="E22" s="14">
+        <v>60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>420</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>180</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08321064-23B5-4B61-ACC3-DCA9BAC814C3}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A208F57F-AAB2-4CCE-B610-44754FED99E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felt a bit tired </t>
+  </si>
+  <si>
+    <t>Utilized the day well</t>
   </si>
 </sst>
 </file>
@@ -1839,48 +1845,96 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>240</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>720</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>30</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A208F57F-AAB2-4CCE-B610-44754FED99E6}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFDBE8A9-0E5F-4ED4-AB2E-262FD9EF8EDA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="77">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Utilized the day well</t>
+  </si>
+  <si>
+    <t>Was having presentation</t>
   </si>
 </sst>
 </file>
@@ -1895,7 +1898,7 @@
         <v>46269</v>
       </c>
       <c r="B24" s="14">
-        <v>720</v>
+        <v>510</v>
       </c>
       <c r="C24" s="14">
         <v>60</v>
@@ -1917,11 +1920,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1350</v>
+        <v>1140</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>26</v>
@@ -1937,114 +1940,234 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>610</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>240</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="14">
+        <v>560</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>360</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>470</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>30</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14">
+        <v>420</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="14">
+        <v>580</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>180</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>460</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>420</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
